--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -552,7 +552,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -640,7 +640,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -662,7 +662,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -684,7 +684,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -703,6 +703,204 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -552,7 +552,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -640,7 +640,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -662,7 +662,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -684,7 +684,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -703,6 +703,204 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,60 +446,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_val_player_start</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_start</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_start</t>
+          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -524,8 +514,6 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -546,8 +534,6 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -568,13 +554,11 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -590,13 +574,11 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -612,13 +594,11 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -634,13 +614,11 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -656,13 +634,11 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -678,8 +654,6 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -700,8 +674,6 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -722,8 +694,6 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -744,8 +714,6 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -766,13 +734,11 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -788,8 +754,6 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -810,13 +774,11 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -832,13 +794,11 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -854,13 +814,11 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -876,8 +834,6 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -898,8 +854,6 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -558,7 +558,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -598,7 +598,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -615,246 +615,6 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>djSMofvg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YZZcMwBs</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>GbeXvnR8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dfO6OQtS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2FREIeA6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>O48oHrZ1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zuzbQnCF</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,60 +436,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -498,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,19 +466,11 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -526,19 +478,11 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -546,19 +490,11 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -566,19 +502,11 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -586,19 +514,11 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -606,14 +526,66 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,30 +563,6 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>x4pn9lxH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -482,7 +482,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>r7j4bXNb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>tI0qkTpo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>WSMotj8U</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>vZqDdBhB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -563,6 +563,78 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>x4pn9lxH</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -479,162 +479,6 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>zsmd0ggn</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>8OhVCWxh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -479,6 +479,90 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,29 +436,59 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -466,11 +496,17 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -478,11 +514,17 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>x4pn9lxH</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -490,11 +532,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -502,11 +550,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tI0qkTpo</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -514,11 +568,17 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r7j4bXNb</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -526,11 +586,17 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WSMotj8U</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -538,11 +604,17 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vZqDdBhB</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -550,11 +622,17 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zsmd0ggn</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -562,6 +640,174 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dQ0zIIKl</t>
+          <t>8OhVCWxh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -521,294 +521,6 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UwsvBA74</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zsmd0ggn</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -521,6 +521,294 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IukqGdk1</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6uSGCr06</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfGPAMUI</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>f18BYPMP</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -614,7 +614,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Q5hiEzKD</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -629,186 +629,6 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2k0SlKj2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,90 +436,326 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.0438511950754519</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0.0438511950754519</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,10 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -484,12 +482,10 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -500,7 +496,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>IukqGdk1</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -511,12 +507,14 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.3120409430391897</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>Q5hiEzKD</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -527,17 +525,17 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.3120409430391897</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -548,12 +546,10 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -564,12 +560,10 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -580,7 +574,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>SfGPAMUI</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -589,7 +583,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.0438511950754519</v>
+        <v>0.6675808001402698</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -598,12 +592,10 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -611,152 +603,6 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>0.0438511950754519</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,116 +493,6 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>0.3120409430391897</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>0.3120409430391897</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>0.6675808001402698</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,62 +436,260 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_sub</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>-0.8071842790439918</v>
+      </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>-0.8071842790439918</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>-0.8071842790439918</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>-0.8071842790439918</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>-0.8071842790439918</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>-0.8071842790439918</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -475,14 +475,14 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-0.8071842790439918</v>
+        <v>-1.355847518354518</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -494,14 +494,14 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-0.8071842790439918</v>
+        <v>-1.355847518354518</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,14 +513,14 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-0.8071842790439918</v>
+        <v>-1.355847518354518</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -532,14 +532,14 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-0.8071842790439918</v>
+        <v>-1.355847518354518</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -551,14 +551,14 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>-0.8071842790439918</v>
+        <v>-1.355847518354518</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -570,53 +570,71 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>-0.8071842790439918</v>
+        <v>-1.355847518354518</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>-1.355847518354518</v>
+      </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>-1.355847518354518</v>
+      </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>-0.4129886178261853</v>
+      </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>-1.355847518354518</v>
+      </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -629,7 +647,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -642,7 +660,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -652,45 +670,6 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,239 +436,414 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>zyC4c6ee</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>ABBmcc1C</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>WQadeyWO</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>MiACepQ7</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rwXP4l3L</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>-0.4129886178261853</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>-1.355847518354518</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>rPiijklS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>nBwH6AY8</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>2mcmYkSq</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,15 +471,10 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_value_player_miss</t>
+          <t>dif_mean_value_player_start</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
@@ -491,9 +486,7 @@
           <t>zyC4c6ee</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -503,7 +496,6 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -511,9 +503,7 @@
           <t>ABBmcc1C</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -523,7 +513,6 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -531,9 +520,7 @@
           <t>WQadeyWO</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -543,7 +530,6 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -551,9 +537,7 @@
           <t>MiACepQ7</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -563,7 +547,6 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -571,9 +554,7 @@
           <t>rwXP4l3L</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -583,17 +564,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -603,17 +581,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -623,17 +598,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -643,7 +615,6 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -651,9 +622,7 @@
           <t>4E8uaJWa</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -663,7 +632,6 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -671,9 +639,7 @@
           <t>rPiijklS</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -683,7 +649,6 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -691,9 +656,7 @@
           <t>nBwH6AY8</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -703,7 +666,6 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -711,9 +673,7 @@
           <t>2mcmYkSq</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -723,7 +683,6 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -731,9 +690,7 @@
           <t>E7rNpTBk</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -743,7 +700,6 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -751,9 +707,7 @@
           <t>Eq0zfXl3</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -763,7 +717,6 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -771,9 +724,7 @@
           <t>M93rhBJF</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -783,7 +734,6 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -791,9 +741,7 @@
           <t>r3GGwC4M</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -803,7 +751,6 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -811,9 +758,7 @@
           <t>fHjVr7t2</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -823,7 +768,6 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -831,9 +775,7 @@
           <t>z1eeWTdd</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -843,7 +785,6 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -514,278 +514,6 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>4E8uaJWa</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nBwH6AY8</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2mcmYkSq</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>r3GGwC4M</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fHjVr7t2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>z1eeWTdd</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -514,6 +514,278 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4E8uaJWa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>zyC4c6ee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>ABBmcc1C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -517,7 +517,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>WQadeyWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -534,7 +534,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>MiACepQ7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -568,7 +568,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -602,7 +602,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>rwXP4l3L</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -633,159 +633,6 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zyC4c6ee</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4E8uaJWa</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -517,7 +517,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -534,7 +534,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -568,7 +568,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -602,7 +602,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -633,6 +633,159 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xMovyDqH</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UkaNveph</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -517,7 +517,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UJQITUyi</t>
+          <t>dr2N9zoI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -534,7 +534,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>j5mWxZE4</t>
+          <t>2q7yHiho</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YmumZjET</t>
+          <t>485V7EFU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -568,7 +568,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>biQrHC9r</t>
+          <t>jVWMBdG5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6HTjFjve</t>
+          <t>8MVuSH0n</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -602,24 +602,36 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0.796277670288843</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.30209174694797</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.85116281135602</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9933740913490257</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8436601763792539</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>v3DAZKP9</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -633,159 +645,6 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -517,24 +517,36 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-0.8134317659432658</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.215080896506857</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.8212456889492932</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.9974191857370105</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.8685258695517454</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -551,7 +563,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -568,7 +580,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -585,7 +597,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -602,36 +614,24 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>0.796277670288843</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.30209174694797</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.85116281135602</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.9933740913490257</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8436601763792539</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>

--- a/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,214 +436,203 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_sub</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xMovyDqH</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UkaNveph</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>-0.8134317659432658</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1.215080896506857</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.8212456889492932</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.9974191857370105</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.8685258695517454</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>j5mWxZE4</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>biQrHC9r</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nee3ysec</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>-0.158175390646688</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YmumZjET</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>v3DAZKP9</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>-0.158175390646688</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
